--- a/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260720_205913.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260720_205913.xlsx
@@ -6440,7 +6440,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6662,7 +6662,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7106,7 +7106,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260720_205913.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_cobasi_20260720_205913.xlsx
@@ -6440,7 +6440,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6662,7 +6662,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7106,7 +7106,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
